--- a/artfynd/A 13767-2026 artfynd.xlsx
+++ b/artfynd/A 13767-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132628286</v>
+        <v>132830448</v>
       </c>
       <c r="B2" t="n">
-        <v>91442</v>
+        <v>92943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>233196</v>
+        <v>4769</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällfotad fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Corner</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Namn, Jmt</t>
+          <t>Namn kalkbarrskog, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481178</v>
+        <v>481196</v>
       </c>
       <c r="R2" t="n">
-        <v>6998245</v>
+        <v>6998276</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,24 +744,24 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-08-30</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Osäker artbestämning</t>
+          <t>1 mycel</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -765,26 +769,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
+          <t>Eva Romell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
+          <t>Eva Romell</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2022</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132830454</v>
+        <v>132830455</v>
       </c>
       <c r="B3" t="n">
-        <v>101340</v>
+        <v>92943</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,24 +796,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Namn kalkbarrskog, Jmt</t>
@@ -846,12 +854,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 mycel</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132830455</v>
+        <v>132830460</v>
       </c>
       <c r="B4" t="n">
-        <v>92880</v>
+        <v>92943</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481167</v>
+        <v>481218</v>
       </c>
       <c r="R4" t="n">
-        <v>6998222</v>
+        <v>6998205</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -951,12 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -992,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132830460</v>
+        <v>132830461</v>
       </c>
       <c r="B5" t="n">
-        <v>92880</v>
+        <v>92943</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481218</v>
+        <v>481251</v>
       </c>
       <c r="R5" t="n">
-        <v>6998205</v>
+        <v>6998232</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1084,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 mycel</t>
+          <t>1 stort mycel, under gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,7 +1118,7 @@
         <v>132830457</v>
       </c>
       <c r="B6" t="n">
-        <v>91446</v>
+        <v>91500</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132830452</v>
+        <v>132830449</v>
       </c>
       <c r="B7" t="n">
-        <v>99470</v>
+        <v>80493</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1223,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219880</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1247,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>481228</v>
+        <v>481212</v>
       </c>
       <c r="R7" t="n">
-        <v>6998228</v>
+        <v>6998305</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,12 +1290,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132830448</v>
+        <v>132830452</v>
       </c>
       <c r="B8" t="n">
-        <v>92880</v>
+        <v>99533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1324,38 +1337,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>219880</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Namn kalkbarrskog, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>481196</v>
+        <v>481228</v>
       </c>
       <c r="R8" t="n">
-        <v>6998276</v>
+        <v>6998228</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,17 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 mycel</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,6 +1422,213 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132830454</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Namn kalkbarrskog, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>481167</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6998222</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Eva Romell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Eva Romell</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132628286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91498</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>233196</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramaria rufescens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Corner</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Namn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>481178</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6998245</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-08-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-08-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Osäker artbestämning</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 13767-2026 artfynd.xlsx
+++ b/artfynd/A 13767-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830448</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830455</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830460</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830461</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830457</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1323,6 +1353,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830449</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830452</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1525,6 +1565,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830454</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,8 +1676,24 @@
           <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132628286</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>